--- a/data.xlsx.xlsx
+++ b/data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yana.k\.cursor\projects\empty-window\nps-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37CC43A-F2E3-4B2B-AF5C-FB0A5F3EE0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCAE778-7BAA-432E-A68C-9D19BD6CE420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{74487427-0345-4DD6-8246-25E85D8ABC71}"/>
   </bookViews>
@@ -1257,6 +1257,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-419]mmmm\ yyyy;@"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1550,17 +1553,17 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1904,7 +1907,7 @@
     <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="98.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6328125" style="49" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6328125" style="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1941,7 +1944,7 @@
       <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="50">
+      <c r="F2" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -1959,7 +1962,7 @@
       <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="50">
+      <c r="F3" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -1979,7 +1982,7 @@
       <c r="E4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="50">
+      <c r="F4" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -1997,7 +2000,7 @@
       <c r="E5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="50">
+      <c r="F5" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2017,7 +2020,7 @@
       <c r="E6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="50">
+      <c r="F6" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2035,7 +2038,7 @@
       <c r="E7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2055,7 +2058,7 @@
       <c r="E8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="50">
+      <c r="F8" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2075,7 +2078,7 @@
       <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="50">
+      <c r="F9" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2093,7 +2096,7 @@
       <c r="E10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2113,7 +2116,7 @@
       <c r="E11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2131,7 +2134,7 @@
       <c r="E12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="50">
+      <c r="F12" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2151,7 +2154,7 @@
       <c r="E13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="50">
+      <c r="F13" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2171,7 +2174,7 @@
       <c r="E14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2189,7 +2192,7 @@
       <c r="E15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="50">
+      <c r="F15" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2207,7 +2210,7 @@
       <c r="E16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="50">
+      <c r="F16" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2225,7 +2228,7 @@
       <c r="E17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F17" s="50">
+      <c r="F17" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2243,7 +2246,7 @@
       <c r="E18" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="50">
+      <c r="F18" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2263,7 +2266,7 @@
       <c r="E19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2281,7 +2284,7 @@
       <c r="E20" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2301,7 +2304,7 @@
       <c r="E21" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="50">
+      <c r="F21" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2321,7 +2324,7 @@
       <c r="E22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F22" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2339,7 +2342,7 @@
       <c r="E23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="50">
+      <c r="F23" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2357,7 +2360,7 @@
       <c r="E24" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="50">
+      <c r="F24" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2375,7 +2378,7 @@
       <c r="E25" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="50">
+      <c r="F25" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2393,7 +2396,7 @@
       <c r="E26" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="50">
+      <c r="F26" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2411,7 +2414,7 @@
       <c r="E27" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F27" s="50">
+      <c r="F27" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2429,7 +2432,7 @@
       <c r="E28" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F28" s="50">
+      <c r="F28" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2447,7 +2450,7 @@
       <c r="E29" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="50">
+      <c r="F29" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2465,7 +2468,7 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="50">
+      <c r="F30" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2483,7 +2486,7 @@
       <c r="E31" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="50">
+      <c r="F31" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2501,7 +2504,7 @@
       <c r="E32" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F32" s="50">
+      <c r="F32" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2519,7 +2522,7 @@
       <c r="E33" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F33" s="50">
+      <c r="F33" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2537,7 +2540,7 @@
       <c r="E34" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F34" s="50">
+      <c r="F34" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2555,7 +2558,7 @@
       <c r="E35" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F35" s="50">
+      <c r="F35" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2573,7 +2576,7 @@
       <c r="E36" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F36" s="50">
+      <c r="F36" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2591,7 +2594,7 @@
       <c r="E37" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F37" s="50">
+      <c r="F37" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2609,7 +2612,7 @@
       <c r="E38" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F38" s="50">
+      <c r="F38" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2627,7 +2630,7 @@
       <c r="E39" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F39" s="50">
+      <c r="F39" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2647,7 +2650,7 @@
       <c r="E40" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="50">
+      <c r="F40" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2665,7 +2668,7 @@
       <c r="E41" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F41" s="50">
+      <c r="F41" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2683,7 +2686,7 @@
       <c r="E42" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F42" s="50">
+      <c r="F42" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2701,7 +2704,7 @@
       <c r="E43" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F43" s="50">
+      <c r="F43" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2719,7 +2722,7 @@
       <c r="E44" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F44" s="50">
+      <c r="F44" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2739,7 +2742,7 @@
       <c r="E45" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F45" s="50">
+      <c r="F45" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2757,7 +2760,7 @@
       <c r="E46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F46" s="50">
+      <c r="F46" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2775,7 +2778,7 @@
       <c r="E47" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F47" s="50">
+      <c r="F47" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2795,7 +2798,7 @@
       <c r="E48" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F48" s="50">
+      <c r="F48" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2815,7 +2818,7 @@
       <c r="E49" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F49" s="50">
+      <c r="F49" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2833,7 +2836,7 @@
       <c r="E50" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F50" s="50">
+      <c r="F50" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2853,7 +2856,7 @@
       <c r="E51" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F51" s="50">
+      <c r="F51" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2871,7 +2874,7 @@
       <c r="E52" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F52" s="50">
+      <c r="F52" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2889,7 +2892,7 @@
       <c r="E53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="50">
+      <c r="F53" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2909,7 +2912,7 @@
       <c r="E54" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F54" s="50">
+      <c r="F54" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2927,7 +2930,7 @@
       <c r="E55" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F55" s="50">
+      <c r="F55" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2945,7 +2948,7 @@
       <c r="E56" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F56" s="50">
+      <c r="F56" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2963,7 +2966,7 @@
       <c r="E57" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F57" s="50">
+      <c r="F57" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2981,7 +2984,7 @@
       <c r="E58" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F58" s="50">
+      <c r="F58" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -2999,7 +3002,7 @@
       <c r="E59" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3019,7 +3022,7 @@
       <c r="E60" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3037,7 +3040,7 @@
       <c r="E61" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3055,7 +3058,7 @@
       <c r="E62" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3073,7 +3076,7 @@
       <c r="E63" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F63" s="50">
+      <c r="F63" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3091,7 +3094,7 @@
       <c r="E64" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F64" s="50">
+      <c r="F64" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3109,7 +3112,7 @@
       <c r="E65" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F65" s="50">
+      <c r="F65" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3129,7 +3132,7 @@
       <c r="E66" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="F66" s="50">
+      <c r="F66" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3147,7 +3150,7 @@
       <c r="E67" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="50">
+      <c r="F67" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3167,7 +3170,7 @@
       <c r="E68" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F68" s="50">
+      <c r="F68" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3185,7 +3188,7 @@
       <c r="E69" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F69" s="50">
+      <c r="F69" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3203,7 +3206,7 @@
       <c r="E70" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F70" s="50">
+      <c r="F70" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3223,7 +3226,7 @@
       <c r="E71" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F71" s="50">
+      <c r="F71" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3241,7 +3244,7 @@
       <c r="E72" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F72" s="50">
+      <c r="F72" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3259,7 +3262,7 @@
       <c r="E73" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F73" s="50">
+      <c r="F73" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3279,7 +3282,7 @@
       <c r="E74" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F74" s="50">
+      <c r="F74" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3299,7 +3302,7 @@
       <c r="E75" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="F75" s="50">
+      <c r="F75" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3317,7 +3320,7 @@
       <c r="E76" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F76" s="50">
+      <c r="F76" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3337,7 +3340,7 @@
       <c r="E77" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F77" s="50">
+      <c r="F77" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3355,7 +3358,7 @@
       <c r="E78" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F78" s="50">
+      <c r="F78" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3373,7 +3376,7 @@
       <c r="E79" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F79" s="50">
+      <c r="F79" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3391,7 +3394,7 @@
       <c r="E80" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F80" s="50">
+      <c r="F80" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3409,7 +3412,7 @@
       <c r="E81" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F81" s="50">
+      <c r="F81" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3427,7 +3430,7 @@
       <c r="E82" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F82" s="50">
+      <c r="F82" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3445,7 +3448,7 @@
       <c r="E83" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F83" s="50">
+      <c r="F83" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3465,7 +3468,7 @@
       <c r="E84" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F84" s="50">
+      <c r="F84" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3485,7 +3488,7 @@
       <c r="E85" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F85" s="50">
+      <c r="F85" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3503,7 +3506,7 @@
       <c r="E86" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F86" s="50">
+      <c r="F86" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3521,7 +3524,7 @@
       <c r="E87" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F87" s="50">
+      <c r="F87" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3539,7 +3542,7 @@
       <c r="E88" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F88" s="50">
+      <c r="F88" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3557,7 +3560,7 @@
       <c r="E89" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F89" s="50">
+      <c r="F89" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3577,7 +3580,7 @@
       <c r="E90" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F90" s="50">
+      <c r="F90" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3595,7 +3598,7 @@
       <c r="E91" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F91" s="50">
+      <c r="F91" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3615,7 +3618,7 @@
       <c r="E92" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F92" s="50">
+      <c r="F92" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3633,7 +3636,7 @@
       <c r="E93" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F93" s="50">
+      <c r="F93" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3651,7 +3654,7 @@
       <c r="E94" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F94" s="50">
+      <c r="F94" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3671,7 +3674,7 @@
       <c r="E95" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="F95" s="50">
+      <c r="F95" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3691,7 +3694,7 @@
       <c r="E96" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F96" s="50">
+      <c r="F96" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3709,7 +3712,7 @@
       <c r="E97" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F97" s="50">
+      <c r="F97" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3727,7 +3730,7 @@
       <c r="E98" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F98" s="50">
+      <c r="F98" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3745,7 +3748,7 @@
       <c r="E99" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F99" s="50">
+      <c r="F99" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3763,7 +3766,7 @@
       <c r="E100" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F100" s="50">
+      <c r="F100" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3783,7 +3786,7 @@
       <c r="E101" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="F101" s="50">
+      <c r="F101" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3801,7 +3804,7 @@
       <c r="E102" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="F102" s="50">
+      <c r="F102" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3819,7 +3822,7 @@
       <c r="E103" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F103" s="50">
+      <c r="F103" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3837,7 +3840,7 @@
       <c r="E104" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F104" s="50">
+      <c r="F104" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3855,7 +3858,7 @@
       <c r="E105" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F105" s="50">
+      <c r="F105" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3873,7 +3876,7 @@
       <c r="E106" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F106" s="50">
+      <c r="F106" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3891,7 +3894,7 @@
       <c r="E107" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F107" s="50">
+      <c r="F107" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3909,7 +3912,7 @@
       <c r="E108" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F108" s="50">
+      <c r="F108" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3927,7 +3930,7 @@
       <c r="E109" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F109" s="50">
+      <c r="F109" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3947,7 +3950,7 @@
       <c r="E110" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F110" s="50">
+      <c r="F110" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3965,7 +3968,7 @@
       <c r="E111" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="F111" s="50">
+      <c r="F111" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -3985,7 +3988,7 @@
       <c r="E112" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="F112" s="50">
+      <c r="F112" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4003,7 +4006,7 @@
       <c r="E113" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F113" s="50">
+      <c r="F113" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4021,7 +4024,7 @@
       <c r="E114" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F114" s="50">
+      <c r="F114" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4039,7 +4042,7 @@
       <c r="E115" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F115" s="50">
+      <c r="F115" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4057,7 +4060,7 @@
       <c r="E116" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F116" s="50">
+      <c r="F116" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4075,7 +4078,7 @@
       <c r="E117" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F117" s="50">
+      <c r="F117" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4093,7 +4096,7 @@
       <c r="E118" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F118" s="50">
+      <c r="F118" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4111,7 +4114,7 @@
       <c r="E119" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F119" s="50">
+      <c r="F119" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4129,7 +4132,7 @@
       <c r="E120" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F120" s="50">
+      <c r="F120" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4147,7 +4150,7 @@
       <c r="E121" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F121" s="50">
+      <c r="F121" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4165,7 +4168,7 @@
       <c r="E122" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F122" s="50">
+      <c r="F122" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4183,7 +4186,7 @@
       <c r="E123" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F123" s="50">
+      <c r="F123" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4201,7 +4204,7 @@
       <c r="E124" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F124" s="50">
+      <c r="F124" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4219,7 +4222,7 @@
       <c r="E125" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F125" s="50">
+      <c r="F125" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4237,7 +4240,7 @@
       <c r="E126" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F126" s="50">
+      <c r="F126" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4255,7 +4258,7 @@
       <c r="E127" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F127" s="50">
+      <c r="F127" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4273,7 +4276,7 @@
       <c r="E128" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F128" s="50">
+      <c r="F128" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4291,7 +4294,7 @@
       <c r="E129" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F129" s="50">
+      <c r="F129" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4311,7 +4314,7 @@
       <c r="E130" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="F130" s="50">
+      <c r="F130" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4329,7 +4332,7 @@
       <c r="E131" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F131" s="50">
+      <c r="F131" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4347,7 +4350,7 @@
       <c r="E132" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F132" s="50">
+      <c r="F132" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4365,7 +4368,7 @@
       <c r="E133" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F133" s="50">
+      <c r="F133" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4383,7 +4386,7 @@
       <c r="E134" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F134" s="50">
+      <c r="F134" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4401,7 +4404,7 @@
       <c r="E135" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F135" s="50">
+      <c r="F135" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4419,7 +4422,7 @@
       <c r="E136" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F136" s="50">
+      <c r="F136" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4437,7 +4440,7 @@
       <c r="E137" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F137" s="50">
+      <c r="F137" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4455,7 +4458,7 @@
       <c r="E138" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F138" s="50">
+      <c r="F138" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4473,7 +4476,7 @@
       <c r="E139" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F139" s="50">
+      <c r="F139" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4491,7 +4494,7 @@
       <c r="E140" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F140" s="50">
+      <c r="F140" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4509,7 +4512,7 @@
       <c r="E141" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="50">
+      <c r="F141" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4527,7 +4530,7 @@
       <c r="E142" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F142" s="50">
+      <c r="F142" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4545,7 +4548,7 @@
       <c r="E143" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F143" s="50">
+      <c r="F143" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4563,7 +4566,7 @@
       <c r="E144" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F144" s="50">
+      <c r="F144" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4581,7 +4584,7 @@
       <c r="E145" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F145" s="50">
+      <c r="F145" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4599,7 +4602,7 @@
       <c r="E146" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F146" s="50">
+      <c r="F146" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4617,7 +4620,7 @@
       <c r="E147" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F147" s="50">
+      <c r="F147" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4635,7 +4638,7 @@
       <c r="E148" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F148" s="50">
+      <c r="F148" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4653,7 +4656,7 @@
       <c r="E149" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F149" s="50">
+      <c r="F149" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4671,7 +4674,7 @@
       <c r="E150" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F150" s="50">
+      <c r="F150" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4689,7 +4692,7 @@
       <c r="E151" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F151" s="50">
+      <c r="F151" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4707,7 +4710,7 @@
       <c r="E152" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F152" s="50">
+      <c r="F152" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4725,7 +4728,7 @@
       <c r="E153" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F153" s="50">
+      <c r="F153" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4743,7 +4746,7 @@
       <c r="E154" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F154" s="50">
+      <c r="F154" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4761,7 +4764,7 @@
       <c r="E155" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F155" s="50">
+      <c r="F155" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4779,7 +4782,7 @@
       <c r="E156" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F156" s="50">
+      <c r="F156" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4797,7 +4800,7 @@
       <c r="E157" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F157" s="50">
+      <c r="F157" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4815,7 +4818,7 @@
       <c r="E158" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F158" s="50">
+      <c r="F158" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4833,7 +4836,7 @@
       <c r="E159" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F159" s="50">
+      <c r="F159" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4853,7 +4856,7 @@
       <c r="E160" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F160" s="50">
+      <c r="F160" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4871,7 +4874,7 @@
       <c r="E161" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F161" s="50">
+      <c r="F161" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4889,7 +4892,7 @@
       <c r="E162" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F162" s="50">
+      <c r="F162" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4907,7 +4910,7 @@
       <c r="E163" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F163" s="50">
+      <c r="F163" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4925,7 +4928,7 @@
       <c r="E164" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F164" s="50">
+      <c r="F164" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4943,7 +4946,7 @@
       <c r="E165" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F165" s="50">
+      <c r="F165" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4961,7 +4964,7 @@
       <c r="E166" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F166" s="50">
+      <c r="F166" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4979,7 +4982,7 @@
       <c r="E167" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F167" s="50">
+      <c r="F167" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -4997,7 +5000,7 @@
       <c r="E168" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F168" s="50">
+      <c r="F168" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5015,7 +5018,7 @@
       <c r="E169" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F169" s="50">
+      <c r="F169" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5033,7 +5036,7 @@
       <c r="E170" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F170" s="50">
+      <c r="F170" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5051,7 +5054,7 @@
       <c r="E171" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F171" s="50">
+      <c r="F171" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5069,7 +5072,7 @@
       <c r="E172" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F172" s="50">
+      <c r="F172" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5087,7 +5090,7 @@
       <c r="E173" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F173" s="50">
+      <c r="F173" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5105,7 +5108,7 @@
       <c r="E174" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F174" s="50">
+      <c r="F174" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5123,7 +5126,7 @@
       <c r="E175" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F175" s="50">
+      <c r="F175" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5141,7 +5144,7 @@
       <c r="E176" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F176" s="50">
+      <c r="F176" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5161,7 +5164,7 @@
       <c r="E177" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F177" s="50">
+      <c r="F177" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5179,7 +5182,7 @@
       <c r="E178" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F178" s="50">
+      <c r="F178" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5197,7 +5200,7 @@
       <c r="E179" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F179" s="50">
+      <c r="F179" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5215,7 +5218,7 @@
       <c r="E180" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F180" s="50">
+      <c r="F180" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5233,7 +5236,7 @@
       <c r="E181" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F181" s="50">
+      <c r="F181" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5251,7 +5254,7 @@
       <c r="E182" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F182" s="50">
+      <c r="F182" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5269,7 +5272,7 @@
       <c r="E183" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F183" s="50">
+      <c r="F183" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5287,7 +5290,7 @@
       <c r="E184" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F184" s="50">
+      <c r="F184" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5307,7 +5310,7 @@
       <c r="E185" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F185" s="50">
+      <c r="F185" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5327,7 +5330,7 @@
       <c r="E186" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F186" s="50">
+      <c r="F186" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5345,7 +5348,7 @@
       <c r="E187" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F187" s="50">
+      <c r="F187" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5363,7 +5366,7 @@
       <c r="E188" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F188" s="50">
+      <c r="F188" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5381,7 +5384,7 @@
       <c r="E189" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F189" s="50">
+      <c r="F189" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5399,7 +5402,7 @@
       <c r="E190" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F190" s="50">
+      <c r="F190" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5417,7 +5420,7 @@
       <c r="E191" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F191" s="50">
+      <c r="F191" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5437,7 +5440,7 @@
       <c r="E192" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F192" s="50">
+      <c r="F192" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5455,7 +5458,7 @@
       <c r="E193" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F193" s="50">
+      <c r="F193" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5473,7 +5476,7 @@
       <c r="E194" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F194" s="50">
+      <c r="F194" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5491,7 +5494,7 @@
       <c r="E195" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F195" s="50">
+      <c r="F195" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5511,7 +5514,7 @@
       <c r="E196" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F196" s="50">
+      <c r="F196" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5529,7 +5532,7 @@
       <c r="E197" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F197" s="50">
+      <c r="F197" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5547,7 +5550,7 @@
       <c r="E198" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F198" s="50">
+      <c r="F198" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5565,7 +5568,7 @@
       <c r="E199" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F199" s="50">
+      <c r="F199" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5583,7 +5586,7 @@
       <c r="E200" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F200" s="50">
+      <c r="F200" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5601,7 +5604,7 @@
       <c r="E201" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F201" s="50">
+      <c r="F201" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5619,7 +5622,7 @@
       <c r="E202" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F202" s="50">
+      <c r="F202" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5637,7 +5640,7 @@
       <c r="E203" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="F203" s="50">
+      <c r="F203" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5655,7 +5658,7 @@
       <c r="E204" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F204" s="50">
+      <c r="F204" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5673,7 +5676,7 @@
       <c r="E205" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F205" s="50">
+      <c r="F205" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5691,7 +5694,7 @@
       <c r="E206" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F206" s="50">
+      <c r="F206" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5709,7 +5712,7 @@
       <c r="E207" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F207" s="50">
+      <c r="F207" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5727,7 +5730,7 @@
       <c r="E208" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F208" s="50">
+      <c r="F208" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5745,7 +5748,7 @@
       <c r="E209" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F209" s="50">
+      <c r="F209" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5763,7 +5766,7 @@
       <c r="E210" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="F210" s="50">
+      <c r="F210" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5781,7 +5784,7 @@
       <c r="E211" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F211" s="50">
+      <c r="F211" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5799,7 +5802,7 @@
       <c r="E212" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F212" s="50">
+      <c r="F212" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5817,7 +5820,7 @@
       <c r="E213" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F213" s="50">
+      <c r="F213" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5835,7 +5838,7 @@
       <c r="E214" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F214" s="50">
+      <c r="F214" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5853,7 +5856,7 @@
       <c r="E215" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F215" s="50">
+      <c r="F215" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5871,7 +5874,7 @@
       <c r="E216" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F216" s="50">
+      <c r="F216" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5889,7 +5892,7 @@
       <c r="E217" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F217" s="50">
+      <c r="F217" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5907,7 +5910,7 @@
       <c r="E218" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F218" s="50">
+      <c r="F218" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5927,7 +5930,7 @@
       <c r="E219" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F219" s="50">
+      <c r="F219" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5945,7 +5948,7 @@
       <c r="E220" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F220" s="50">
+      <c r="F220" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5963,7 +5966,7 @@
       <c r="E221" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F221" s="50">
+      <c r="F221" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5981,7 +5984,7 @@
       <c r="E222" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F222" s="50">
+      <c r="F222" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -5999,7 +6002,7 @@
       <c r="E223" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F223" s="50">
+      <c r="F223" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6017,7 +6020,7 @@
       <c r="E224" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F224" s="50">
+      <c r="F224" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6035,7 +6038,7 @@
       <c r="E225" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F225" s="50">
+      <c r="F225" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6053,7 +6056,7 @@
       <c r="E226" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F226" s="50">
+      <c r="F226" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6073,7 +6076,7 @@
       <c r="E227" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F227" s="50">
+      <c r="F227" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6091,7 +6094,7 @@
       <c r="E228" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F228" s="50">
+      <c r="F228" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6109,7 +6112,7 @@
       <c r="E229" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F229" s="50">
+      <c r="F229" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6127,7 +6130,7 @@
       <c r="E230" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F230" s="50">
+      <c r="F230" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6145,7 +6148,7 @@
       <c r="E231" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F231" s="50">
+      <c r="F231" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6163,7 +6166,7 @@
       <c r="E232" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F232" s="50">
+      <c r="F232" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6181,7 +6184,7 @@
       <c r="E233" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F233" s="50">
+      <c r="F233" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6199,7 +6202,7 @@
       <c r="E234" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F234" s="50">
+      <c r="F234" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6217,7 +6220,7 @@
       <c r="E235" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F235" s="50">
+      <c r="F235" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6235,7 +6238,7 @@
       <c r="E236" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F236" s="50">
+      <c r="F236" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6253,7 +6256,7 @@
       <c r="E237" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F237" s="50">
+      <c r="F237" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6273,7 +6276,7 @@
       <c r="E238" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F238" s="50">
+      <c r="F238" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6291,7 +6294,7 @@
       <c r="E239" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F239" s="50">
+      <c r="F239" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6309,7 +6312,7 @@
       <c r="E240" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F240" s="50">
+      <c r="F240" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6327,7 +6330,7 @@
       <c r="E241" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F241" s="50">
+      <c r="F241" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6345,7 +6348,7 @@
       <c r="E242" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F242" s="50">
+      <c r="F242" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6363,7 +6366,7 @@
       <c r="E243" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F243" s="50">
+      <c r="F243" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6381,7 +6384,7 @@
       <c r="E244" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F244" s="50">
+      <c r="F244" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6401,7 +6404,7 @@
       <c r="E245" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F245" s="50">
+      <c r="F245" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6419,7 +6422,7 @@
       <c r="E246" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="F246" s="50">
+      <c r="F246" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6437,7 +6440,7 @@
       <c r="E247" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F247" s="50">
+      <c r="F247" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6455,7 +6458,7 @@
       <c r="E248" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F248" s="50">
+      <c r="F248" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6475,7 +6478,7 @@
       <c r="E249" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="F249" s="50">
+      <c r="F249" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6493,7 +6496,7 @@
       <c r="E250" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F250" s="50">
+      <c r="F250" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6511,7 +6514,7 @@
       <c r="E251" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F251" s="50">
+      <c r="F251" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6529,7 +6532,7 @@
       <c r="E252" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F252" s="50">
+      <c r="F252" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6547,7 +6550,7 @@
       <c r="E253" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F253" s="50">
+      <c r="F253" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6565,7 +6568,7 @@
       <c r="E254" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F254" s="50">
+      <c r="F254" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6585,7 +6588,7 @@
       <c r="E255" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F255" s="50">
+      <c r="F255" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6603,7 +6606,7 @@
       <c r="E256" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F256" s="50">
+      <c r="F256" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6621,7 +6624,7 @@
       <c r="E257" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F257" s="50">
+      <c r="F257" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6639,7 +6642,7 @@
       <c r="E258" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F258" s="50">
+      <c r="F258" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6657,7 +6660,7 @@
       <c r="E259" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="F259" s="50">
+      <c r="F259" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6675,7 +6678,7 @@
       <c r="E260" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F260" s="50">
+      <c r="F260" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6695,7 +6698,7 @@
       <c r="E261" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F261" s="50">
+      <c r="F261" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6713,7 +6716,7 @@
       <c r="E262" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F262" s="50">
+      <c r="F262" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6731,7 +6734,7 @@
       <c r="E263" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F263" s="50">
+      <c r="F263" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6749,7 +6752,7 @@
       <c r="E264" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F264" s="50">
+      <c r="F264" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6767,7 +6770,7 @@
       <c r="E265" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F265" s="50">
+      <c r="F265" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6785,7 +6788,7 @@
       <c r="E266" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F266" s="50">
+      <c r="F266" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6805,7 +6808,7 @@
       <c r="E267" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F267" s="50">
+      <c r="F267" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6823,7 +6826,7 @@
       <c r="E268" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F268" s="50">
+      <c r="F268" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6841,7 +6844,7 @@
       <c r="E269" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F269" s="50">
+      <c r="F269" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6859,7 +6862,7 @@
       <c r="E270" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F270" s="50">
+      <c r="F270" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6879,7 +6882,7 @@
       <c r="E271" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F271" s="50">
+      <c r="F271" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6897,7 +6900,7 @@
       <c r="E272" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F272" s="50">
+      <c r="F272" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6915,7 +6918,7 @@
       <c r="E273" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F273" s="50">
+      <c r="F273" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6933,7 +6936,7 @@
       <c r="E274" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F274" s="50">
+      <c r="F274" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6951,7 +6954,7 @@
       <c r="E275" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F275" s="50">
+      <c r="F275" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6969,7 +6972,7 @@
       <c r="E276" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F276" s="50">
+      <c r="F276" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -6987,7 +6990,7 @@
       <c r="E277" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F277" s="50">
+      <c r="F277" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7005,7 +7008,7 @@
       <c r="E278" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F278" s="50">
+      <c r="F278" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7023,7 +7026,7 @@
       <c r="E279" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F279" s="50">
+      <c r="F279" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7041,7 +7044,7 @@
       <c r="E280" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F280" s="50">
+      <c r="F280" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7059,7 +7062,7 @@
       <c r="E281" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F281" s="50">
+      <c r="F281" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7079,7 +7082,7 @@
       <c r="E282" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F282" s="50">
+      <c r="F282" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7097,7 +7100,7 @@
       <c r="E283" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F283" s="50">
+      <c r="F283" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7117,7 +7120,7 @@
       <c r="E284" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F284" s="50">
+      <c r="F284" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7137,7 +7140,7 @@
       <c r="E285" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F285" s="50">
+      <c r="F285" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7155,7 +7158,7 @@
       <c r="E286" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F286" s="50">
+      <c r="F286" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7173,7 +7176,7 @@
       <c r="E287" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F287" s="50">
+      <c r="F287" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7193,7 +7196,7 @@
       <c r="E288" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F288" s="50">
+      <c r="F288" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7211,7 +7214,7 @@
       <c r="E289" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F289" s="50">
+      <c r="F289" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7229,7 +7232,7 @@
       <c r="E290" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F290" s="50">
+      <c r="F290" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7247,7 +7250,7 @@
       <c r="E291" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F291" s="50">
+      <c r="F291" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7265,7 +7268,7 @@
       <c r="E292" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F292" s="50">
+      <c r="F292" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7285,7 +7288,7 @@
       <c r="E293" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F293" s="50">
+      <c r="F293" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7303,7 +7306,7 @@
       <c r="E294" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F294" s="50">
+      <c r="F294" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7323,7 +7326,7 @@
       <c r="E295" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="F295" s="50">
+      <c r="F295" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7343,7 +7346,7 @@
       <c r="E296" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="F296" s="50">
+      <c r="F296" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7361,7 +7364,7 @@
       <c r="E297" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F297" s="50">
+      <c r="F297" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7379,7 +7382,7 @@
       <c r="E298" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F298" s="50">
+      <c r="F298" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7399,7 +7402,7 @@
       <c r="E299" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F299" s="50">
+      <c r="F299" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7417,7 +7420,7 @@
       <c r="E300" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F300" s="50">
+      <c r="F300" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7435,7 +7438,7 @@
       <c r="E301" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F301" s="50">
+      <c r="F301" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7453,7 +7456,7 @@
       <c r="E302" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F302" s="50">
+      <c r="F302" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7471,7 +7474,7 @@
       <c r="E303" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F303" s="50">
+      <c r="F303" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7491,7 +7494,7 @@
       <c r="E304" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F304" s="50">
+      <c r="F304" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7509,7 +7512,7 @@
       <c r="E305" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F305" s="50">
+      <c r="F305" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7527,7 +7530,7 @@
       <c r="E306" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F306" s="50">
+      <c r="F306" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7545,7 +7548,7 @@
       <c r="E307" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F307" s="50">
+      <c r="F307" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7563,7 +7566,7 @@
       <c r="E308" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F308" s="50">
+      <c r="F308" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7581,7 +7584,7 @@
       <c r="E309" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F309" s="50">
+      <c r="F309" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7599,7 +7602,7 @@
       <c r="E310" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F310" s="50">
+      <c r="F310" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7617,7 +7620,7 @@
       <c r="E311" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="F311" s="50">
+      <c r="F311" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7637,7 +7640,7 @@
       <c r="E312" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F312" s="50">
+      <c r="F312" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7655,7 +7658,7 @@
       <c r="E313" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F313" s="50">
+      <c r="F313" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7673,7 +7676,7 @@
       <c r="E314" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F314" s="50">
+      <c r="F314" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7691,7 +7694,7 @@
       <c r="E315" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F315" s="50">
+      <c r="F315" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7709,7 +7712,7 @@
       <c r="E316" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F316" s="50">
+      <c r="F316" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7727,7 +7730,7 @@
       <c r="E317" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F317" s="50">
+      <c r="F317" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7745,7 +7748,7 @@
       <c r="E318" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F318" s="50">
+      <c r="F318" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7765,7 +7768,7 @@
       <c r="E319" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F319" s="50">
+      <c r="F319" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7785,7 +7788,7 @@
       <c r="E320" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="F320" s="50">
+      <c r="F320" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7803,7 +7806,7 @@
       <c r="E321" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F321" s="50">
+      <c r="F321" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7823,7 +7826,7 @@
       <c r="E322" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F322" s="50">
+      <c r="F322" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7843,7 +7846,7 @@
       <c r="E323" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F323" s="50">
+      <c r="F323" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7861,7 +7864,7 @@
       <c r="E324" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F324" s="50">
+      <c r="F324" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7879,7 +7882,7 @@
       <c r="E325" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F325" s="50">
+      <c r="F325" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7899,7 +7902,7 @@
       <c r="E326" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F326" s="50">
+      <c r="F326" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7917,7 +7920,7 @@
       <c r="E327" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F327" s="50">
+      <c r="F327" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7935,7 +7938,7 @@
       <c r="E328" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F328" s="50">
+      <c r="F328" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7953,7 +7956,7 @@
       <c r="E329" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F329" s="50">
+      <c r="F329" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7971,7 +7974,7 @@
       <c r="E330" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F330" s="50">
+      <c r="F330" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -7989,7 +7992,7 @@
       <c r="E331" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F331" s="50">
+      <c r="F331" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8009,7 +8012,7 @@
       <c r="E332" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F332" s="50">
+      <c r="F332" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8027,7 +8030,7 @@
       <c r="E333" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F333" s="50">
+      <c r="F333" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8045,7 +8048,7 @@
       <c r="E334" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F334" s="50">
+      <c r="F334" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8063,7 +8066,7 @@
       <c r="E335" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F335" s="50">
+      <c r="F335" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8081,7 +8084,7 @@
       <c r="E336" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F336" s="50">
+      <c r="F336" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8099,7 +8102,7 @@
       <c r="E337" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F337" s="50">
+      <c r="F337" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8119,7 +8122,7 @@
       <c r="E338" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="F338" s="50">
+      <c r="F338" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8139,7 +8142,7 @@
       <c r="E339" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="F339" s="50">
+      <c r="F339" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8159,7 +8162,7 @@
       <c r="E340" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="F340" s="50">
+      <c r="F340" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8177,7 +8180,7 @@
       <c r="E341" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F341" s="50">
+      <c r="F341" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8195,7 +8198,7 @@
       <c r="E342" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F342" s="50">
+      <c r="F342" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8213,7 +8216,7 @@
       <c r="E343" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="F343" s="50">
+      <c r="F343" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8233,7 +8236,7 @@
       <c r="E344" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="F344" s="50">
+      <c r="F344" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8251,7 +8254,7 @@
       <c r="E345" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F345" s="50">
+      <c r="F345" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8269,7 +8272,7 @@
       <c r="E346" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F346" s="50">
+      <c r="F346" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8287,7 +8290,7 @@
       <c r="E347" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F347" s="50">
+      <c r="F347" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8305,7 +8308,7 @@
       <c r="E348" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F348" s="50">
+      <c r="F348" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8325,7 +8328,7 @@
       <c r="E349" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="F349" s="50">
+      <c r="F349" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8343,7 +8346,7 @@
       <c r="E350" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F350" s="50">
+      <c r="F350" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8361,7 +8364,7 @@
       <c r="E351" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="F351" s="50">
+      <c r="F351" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8381,7 +8384,7 @@
       <c r="E352" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="F352" s="50">
+      <c r="F352" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8399,7 +8402,7 @@
       <c r="E353" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F353" s="50">
+      <c r="F353" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8417,7 +8420,7 @@
       <c r="E354" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F354" s="50">
+      <c r="F354" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8435,7 +8438,7 @@
       <c r="E355" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F355" s="50">
+      <c r="F355" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8453,7 +8456,7 @@
       <c r="E356" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F356" s="50">
+      <c r="F356" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8471,7 +8474,7 @@
       <c r="E357" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="F357" s="50">
+      <c r="F357" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8489,7 +8492,7 @@
       <c r="E358" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F358" s="50">
+      <c r="F358" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8509,7 +8512,7 @@
       <c r="E359" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="F359" s="50">
+      <c r="F359" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8527,7 +8530,7 @@
       <c r="E360" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="F360" s="50">
+      <c r="F360" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8545,7 +8548,7 @@
       <c r="E361" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="F361" s="50">
+      <c r="F361" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8563,7 +8566,7 @@
       <c r="E362" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F362" s="50">
+      <c r="F362" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8581,7 +8584,7 @@
       <c r="E363" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="F363" s="50">
+      <c r="F363" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8599,7 +8602,7 @@
       <c r="E364" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F364" s="50">
+      <c r="F364" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8619,7 +8622,7 @@
       <c r="E365" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="F365" s="50">
+      <c r="F365" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8637,7 +8640,7 @@
       <c r="E366" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="F366" s="50">
+      <c r="F366" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8655,7 +8658,7 @@
       <c r="E367" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="F367" s="50">
+      <c r="F367" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8673,7 +8676,7 @@
       <c r="E368" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="F368" s="50">
+      <c r="F368" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8691,7 +8694,7 @@
       <c r="E369" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="F369" s="50">
+      <c r="F369" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8711,7 +8714,7 @@
       <c r="E370" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F370" s="50">
+      <c r="F370" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8731,7 +8734,7 @@
       <c r="E371" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F371" s="50">
+      <c r="F371" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8751,7 +8754,7 @@
       <c r="E372" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="F372" s="50">
+      <c r="F372" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8771,7 +8774,7 @@
       <c r="E373" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F373" s="50">
+      <c r="F373" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8789,7 +8792,7 @@
       <c r="E374" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="F374" s="50">
+      <c r="F374" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8807,7 +8810,7 @@
       <c r="E375" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F375" s="50">
+      <c r="F375" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8825,7 +8828,7 @@
       <c r="E376" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F376" s="50">
+      <c r="F376" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8845,7 +8848,7 @@
       <c r="E377" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="F377" s="50">
+      <c r="F377" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8863,7 +8866,7 @@
       <c r="E378" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F378" s="50">
+      <c r="F378" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8881,7 +8884,7 @@
       <c r="E379" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F379" s="50">
+      <c r="F379" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8899,7 +8902,7 @@
       <c r="E380" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F380" s="50">
+      <c r="F380" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8917,7 +8920,7 @@
       <c r="E381" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F381" s="50">
+      <c r="F381" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8937,7 +8940,7 @@
       <c r="E382" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F382" s="50">
+      <c r="F382" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8955,7 +8958,7 @@
       <c r="E383" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F383" s="50">
+      <c r="F383" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8975,7 +8978,7 @@
       <c r="E384" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F384" s="50">
+      <c r="F384" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -8993,7 +8996,7 @@
       <c r="E385" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F385" s="50">
+      <c r="F385" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9011,7 +9014,7 @@
       <c r="E386" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F386" s="50">
+      <c r="F386" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9029,7 +9032,7 @@
       <c r="E387" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="F387" s="50">
+      <c r="F387" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9047,7 +9050,7 @@
       <c r="E388" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F388" s="50">
+      <c r="F388" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9065,7 +9068,7 @@
       <c r="E389" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="F389" s="50">
+      <c r="F389" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9083,7 +9086,7 @@
       <c r="E390" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F390" s="50">
+      <c r="F390" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9101,7 +9104,7 @@
       <c r="E391" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F391" s="50">
+      <c r="F391" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9119,7 +9122,7 @@
       <c r="E392" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="F392" s="50">
+      <c r="F392" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9139,7 +9142,7 @@
       <c r="E393" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="F393" s="50">
+      <c r="F393" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9157,7 +9160,7 @@
       <c r="E394" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F394" s="50">
+      <c r="F394" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9175,7 +9178,7 @@
       <c r="E395" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F395" s="50">
+      <c r="F395" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9193,7 +9196,7 @@
       <c r="E396" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F396" s="50">
+      <c r="F396" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9211,7 +9214,7 @@
       <c r="E397" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F397" s="50">
+      <c r="F397" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9229,7 +9232,7 @@
       <c r="E398" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F398" s="50">
+      <c r="F398" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9247,7 +9250,7 @@
       <c r="E399" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F399" s="50">
+      <c r="F399" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9265,7 +9268,7 @@
       <c r="E400" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F400" s="50">
+      <c r="F400" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9283,7 +9286,7 @@
       <c r="E401" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F401" s="50">
+      <c r="F401" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9301,7 +9304,7 @@
       <c r="E402" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F402" s="50">
+      <c r="F402" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9321,7 +9324,7 @@
       <c r="E403" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F403" s="50">
+      <c r="F403" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9339,7 +9342,7 @@
       <c r="E404" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="F404" s="50">
+      <c r="F404" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9357,7 +9360,7 @@
       <c r="E405" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F405" s="50">
+      <c r="F405" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9377,7 +9380,7 @@
       <c r="E406" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F406" s="50">
+      <c r="F406" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9397,7 +9400,7 @@
       <c r="E407" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F407" s="50">
+      <c r="F407" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9415,7 +9418,7 @@
       <c r="E408" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F408" s="50">
+      <c r="F408" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9435,7 +9438,7 @@
       <c r="E409" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F409" s="50">
+      <c r="F409" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9455,7 +9458,7 @@
       <c r="E410" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="F410" s="50">
+      <c r="F410" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9473,7 +9476,7 @@
       <c r="E411" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F411" s="50">
+      <c r="F411" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9491,7 +9494,7 @@
       <c r="E412" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F412" s="50">
+      <c r="F412" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9509,7 +9512,7 @@
       <c r="E413" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="F413" s="50">
+      <c r="F413" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9527,7 +9530,7 @@
       <c r="E414" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F414" s="50">
+      <c r="F414" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9545,7 +9548,7 @@
       <c r="E415" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F415" s="50">
+      <c r="F415" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9565,7 +9568,7 @@
       <c r="E416" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F416" s="50">
+      <c r="F416" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9583,7 +9586,7 @@
       <c r="E417" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F417" s="50">
+      <c r="F417" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9601,7 +9604,7 @@
       <c r="E418" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F418" s="50">
+      <c r="F418" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9619,7 +9622,7 @@
       <c r="E419" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F419" s="50">
+      <c r="F419" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9639,7 +9642,7 @@
       <c r="E420" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="F420" s="50">
+      <c r="F420" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9657,7 +9660,7 @@
       <c r="E421" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F421" s="50">
+      <c r="F421" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9675,7 +9678,7 @@
       <c r="E422" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F422" s="50">
+      <c r="F422" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9693,7 +9696,7 @@
       <c r="E423" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F423" s="50">
+      <c r="F423" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9713,7 +9716,7 @@
       <c r="E424" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F424" s="50">
+      <c r="F424" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9731,7 +9734,7 @@
       <c r="E425" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F425" s="50">
+      <c r="F425" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9751,7 +9754,7 @@
       <c r="E426" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F426" s="50">
+      <c r="F426" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9769,7 +9772,7 @@
       <c r="E427" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F427" s="50">
+      <c r="F427" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9787,7 +9790,7 @@
       <c r="E428" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F428" s="50">
+      <c r="F428" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9805,7 +9808,7 @@
       <c r="E429" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F429" s="50">
+      <c r="F429" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9823,7 +9826,7 @@
       <c r="E430" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F430" s="50">
+      <c r="F430" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9841,7 +9844,7 @@
       <c r="E431" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F431" s="50">
+      <c r="F431" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9859,7 +9862,7 @@
       <c r="E432" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F432" s="50">
+      <c r="F432" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9877,7 +9880,7 @@
       <c r="E433" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F433" s="50">
+      <c r="F433" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9895,7 +9898,7 @@
       <c r="E434" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F434" s="50">
+      <c r="F434" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9913,7 +9916,7 @@
       <c r="E435" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F435" s="50">
+      <c r="F435" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9933,7 +9936,7 @@
       <c r="E436" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F436" s="50">
+      <c r="F436" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9951,7 +9954,7 @@
       <c r="E437" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F437" s="50">
+      <c r="F437" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9971,7 +9974,7 @@
       <c r="E438" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F438" s="50">
+      <c r="F438" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -9989,7 +9992,7 @@
       <c r="E439" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F439" s="50">
+      <c r="F439" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10007,7 +10010,7 @@
       <c r="E440" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F440" s="50">
+      <c r="F440" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10025,7 +10028,7 @@
       <c r="E441" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F441" s="50">
+      <c r="F441" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10043,7 +10046,7 @@
       <c r="E442" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F442" s="50">
+      <c r="F442" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10061,7 +10064,7 @@
       <c r="E443" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F443" s="50">
+      <c r="F443" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10081,7 +10084,7 @@
       <c r="E444" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F444" s="50">
+      <c r="F444" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10099,7 +10102,7 @@
       <c r="E445" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F445" s="50">
+      <c r="F445" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10117,7 +10120,7 @@
       <c r="E446" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F446" s="50">
+      <c r="F446" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10135,7 +10138,7 @@
       <c r="E447" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="F447" s="50">
+      <c r="F447" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10153,7 +10156,7 @@
       <c r="E448" s="37" t="s">
         <v>264</v>
       </c>
-      <c r="F448" s="50">
+      <c r="F448" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10173,7 +10176,7 @@
       <c r="E449" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F449" s="50">
+      <c r="F449" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10191,7 +10194,7 @@
       <c r="E450" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F450" s="50">
+      <c r="F450" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10209,7 +10212,7 @@
       <c r="E451" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F451" s="50">
+      <c r="F451" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10227,7 +10230,7 @@
       <c r="E452" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F452" s="50">
+      <c r="F452" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10245,7 +10248,7 @@
       <c r="E453" s="37" t="s">
         <v>265</v>
       </c>
-      <c r="F453" s="50">
+      <c r="F453" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10263,7 +10266,7 @@
       <c r="E454" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F454" s="50">
+      <c r="F454" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10281,7 +10284,7 @@
       <c r="E455" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="F455" s="50">
+      <c r="F455" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10301,7 +10304,7 @@
       <c r="E456" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F456" s="50">
+      <c r="F456" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10321,7 +10324,7 @@
       <c r="E457" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F457" s="50">
+      <c r="F457" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10341,7 +10344,7 @@
       <c r="E458" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F458" s="50">
+      <c r="F458" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10359,7 +10362,7 @@
       <c r="E459" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F459" s="50">
+      <c r="F459" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10377,7 +10380,7 @@
       <c r="E460" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="F460" s="50">
+      <c r="F460" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10395,7 +10398,7 @@
       <c r="E461" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="F461" s="50">
+      <c r="F461" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10413,7 +10416,7 @@
       <c r="E462" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F462" s="50">
+      <c r="F462" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10433,7 +10436,7 @@
       <c r="E463" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F463" s="50">
+      <c r="F463" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10451,7 +10454,7 @@
       <c r="E464" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F464" s="50">
+      <c r="F464" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10469,7 +10472,7 @@
       <c r="E465" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F465" s="50">
+      <c r="F465" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10487,7 +10490,7 @@
       <c r="E466" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F466" s="50">
+      <c r="F466" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10505,7 +10508,7 @@
       <c r="E467" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F467" s="50">
+      <c r="F467" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10523,7 +10526,7 @@
       <c r="E468" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F468" s="50">
+      <c r="F468" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10541,7 +10544,7 @@
       <c r="E469" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F469" s="50">
+      <c r="F469" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10559,7 +10562,7 @@
       <c r="E470" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F470" s="50">
+      <c r="F470" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10577,7 +10580,7 @@
       <c r="E471" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F471" s="50">
+      <c r="F471" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10597,7 +10600,7 @@
       <c r="E472" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F472" s="50">
+      <c r="F472" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10617,7 +10620,7 @@
       <c r="E473" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F473" s="50">
+      <c r="F473" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10635,7 +10638,7 @@
       <c r="E474" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F474" s="50">
+      <c r="F474" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10653,7 +10656,7 @@
       <c r="E475" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F475" s="50">
+      <c r="F475" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10671,7 +10674,7 @@
       <c r="E476" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F476" s="50">
+      <c r="F476" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10689,7 +10692,7 @@
       <c r="E477" t="s">
         <v>269</v>
       </c>
-      <c r="F477" s="50">
+      <c r="F477" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10707,7 +10710,7 @@
       <c r="E478" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="F478" s="50">
+      <c r="F478" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10725,7 +10728,7 @@
       <c r="E479" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F479" s="50">
+      <c r="F479" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10745,7 +10748,7 @@
       <c r="E480" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F480" s="50">
+      <c r="F480" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10763,7 +10766,7 @@
       <c r="E481" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F481" s="50">
+      <c r="F481" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10781,7 +10784,7 @@
       <c r="E482" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F482" s="50">
+      <c r="F482" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10799,7 +10802,7 @@
       <c r="E483" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F483" s="50">
+      <c r="F483" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10817,7 +10820,7 @@
       <c r="E484" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F484" s="50">
+      <c r="F484" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10835,7 +10838,7 @@
       <c r="E485" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F485" s="50">
+      <c r="F485" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10853,7 +10856,7 @@
       <c r="E486" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F486" s="50">
+      <c r="F486" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10871,7 +10874,7 @@
       <c r="E487" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F487" s="50">
+      <c r="F487" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10889,7 +10892,7 @@
       <c r="E488" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F488" s="50">
+      <c r="F488" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10907,7 +10910,7 @@
       <c r="E489" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F489" s="50">
+      <c r="F489" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10927,7 +10930,7 @@
       <c r="E490" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F490" s="50">
+      <c r="F490" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10945,7 +10948,7 @@
       <c r="E491" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F491" s="50">
+      <c r="F491" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10963,7 +10966,7 @@
       <c r="E492" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F492" s="50">
+      <c r="F492" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10981,7 +10984,7 @@
       <c r="E493" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F493" s="50">
+      <c r="F493" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -10999,7 +11002,7 @@
       <c r="E494" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F494" s="50">
+      <c r="F494" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -11017,7 +11020,7 @@
       <c r="E495" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F495" s="50">
+      <c r="F495" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -11037,7 +11040,7 @@
       <c r="E496" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="F496" s="50">
+      <c r="F496" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -11057,7 +11060,7 @@
       <c r="E497" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F497" s="50">
+      <c r="F497" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -11075,7 +11078,7 @@
       <c r="E498" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F498" s="50">
+      <c r="F498" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -11093,7 +11096,7 @@
       <c r="E499" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F499" s="50">
+      <c r="F499" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -11111,7 +11114,7 @@
       <c r="E500" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F500" s="50">
+      <c r="F500" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -11129,7 +11132,7 @@
       <c r="E501" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F501" s="50">
+      <c r="F501" s="48">
         <v>46113</v>
       </c>
     </row>
@@ -11147,7 +11150,7 @@
       <c r="E502" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F502" s="48">
+      <c r="F502" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11165,7 +11168,7 @@
       <c r="E503" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F503" s="48">
+      <c r="F503" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11183,7 +11186,7 @@
       <c r="E504" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F504" s="48">
+      <c r="F504" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11201,7 +11204,7 @@
       <c r="E505" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F505" s="48">
+      <c r="F505" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11219,7 +11222,7 @@
       <c r="E506" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="F506" s="48">
+      <c r="F506" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11237,7 +11240,7 @@
       <c r="E507" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F507" s="48">
+      <c r="F507" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11255,7 +11258,7 @@
       <c r="E508" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F508" s="48">
+      <c r="F508" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11273,7 +11276,7 @@
       <c r="E509" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F509" s="48">
+      <c r="F509" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11291,7 +11294,7 @@
       <c r="E510" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F510" s="48">
+      <c r="F510" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11311,7 +11314,7 @@
       <c r="E511" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="F511" s="48">
+      <c r="F511" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11329,7 +11332,7 @@
       <c r="E512" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F512" s="48">
+      <c r="F512" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11347,7 +11350,7 @@
       <c r="E513" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F513" s="48">
+      <c r="F513" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11365,7 +11368,7 @@
       <c r="E514" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F514" s="48">
+      <c r="F514" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11383,7 +11386,7 @@
       <c r="E515" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F515" s="48">
+      <c r="F515" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11401,7 +11404,7 @@
       <c r="E516" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F516" s="48">
+      <c r="F516" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11419,7 +11422,7 @@
       <c r="E517" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F517" s="48">
+      <c r="F517" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11437,7 +11440,7 @@
       <c r="E518" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F518" s="48">
+      <c r="F518" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11455,7 +11458,7 @@
       <c r="E519" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F519" s="48">
+      <c r="F519" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11473,7 +11476,7 @@
       <c r="E520" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="F520" s="48">
+      <c r="F520" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11493,7 +11496,7 @@
       <c r="E521" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="F521" s="48">
+      <c r="F521" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11511,7 +11514,7 @@
       <c r="E522" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="F522" s="48">
+      <c r="F522" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11529,7 +11532,7 @@
       <c r="E523" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F523" s="48">
+      <c r="F523" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11547,7 +11550,7 @@
       <c r="E524" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F524" s="48">
+      <c r="F524" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11567,7 +11570,7 @@
       <c r="E525" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="F525" s="48">
+      <c r="F525" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11587,7 +11590,7 @@
       <c r="E526" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F526" s="48">
+      <c r="F526" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11605,7 +11608,7 @@
       <c r="E527" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F527" s="48">
+      <c r="F527" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11623,7 +11626,7 @@
       <c r="E528" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F528" s="48">
+      <c r="F528" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11641,7 +11644,7 @@
       <c r="E529" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F529" s="48">
+      <c r="F529" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11659,7 +11662,7 @@
       <c r="E530" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="F530" s="48">
+      <c r="F530" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11677,7 +11680,7 @@
       <c r="E531" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F531" s="48">
+      <c r="F531" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11695,7 +11698,7 @@
       <c r="E532" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F532" s="48">
+      <c r="F532" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11715,7 +11718,7 @@
       <c r="E533" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F533" s="48">
+      <c r="F533" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11733,7 +11736,7 @@
       <c r="E534" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F534" s="48">
+      <c r="F534" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11751,7 +11754,7 @@
       <c r="E535" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F535" s="48">
+      <c r="F535" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11771,7 +11774,7 @@
       <c r="E536" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F536" s="48">
+      <c r="F536" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11791,7 +11794,7 @@
       <c r="E537" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="F537" s="48">
+      <c r="F537" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11809,7 +11812,7 @@
       <c r="E538" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F538" s="48">
+      <c r="F538" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11827,7 +11830,7 @@
       <c r="E539" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F539" s="48">
+      <c r="F539" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11847,7 +11850,7 @@
       <c r="E540" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F540" s="48">
+      <c r="F540" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11867,7 +11870,7 @@
       <c r="E541" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F541" s="48">
+      <c r="F541" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11885,7 +11888,7 @@
       <c r="E542" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F542" s="48">
+      <c r="F542" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11905,7 +11908,7 @@
       <c r="E543" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F543" s="48">
+      <c r="F543" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11923,7 +11926,7 @@
       <c r="E544" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F544" s="48">
+      <c r="F544" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11941,7 +11944,7 @@
       <c r="E545" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F545" s="48">
+      <c r="F545" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11959,7 +11962,7 @@
       <c r="E546" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F546" s="48">
+      <c r="F546" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11977,7 +11980,7 @@
       <c r="E547" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F547" s="48">
+      <c r="F547" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -11995,7 +11998,7 @@
       <c r="E548" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F548" s="48">
+      <c r="F548" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12013,7 +12016,7 @@
       <c r="E549" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F549" s="48">
+      <c r="F549" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12033,7 +12036,7 @@
       <c r="E550" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F550" s="48">
+      <c r="F550" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12053,7 +12056,7 @@
       <c r="E551" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F551" s="48">
+      <c r="F551" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12071,7 +12074,7 @@
       <c r="E552" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="F552" s="48">
+      <c r="F552" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12089,7 +12092,7 @@
       <c r="E553" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F553" s="48">
+      <c r="F553" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12107,7 +12110,7 @@
       <c r="E554" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F554" s="48">
+      <c r="F554" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12125,7 +12128,7 @@
       <c r="E555" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="F555" s="48">
+      <c r="F555" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12145,7 +12148,7 @@
       <c r="E556" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F556" s="48">
+      <c r="F556" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12165,7 +12168,7 @@
       <c r="E557" s="34" t="s">
         <v>298</v>
       </c>
-      <c r="F557" s="48">
+      <c r="F557" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12185,7 +12188,7 @@
       <c r="E558" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F558" s="48">
+      <c r="F558" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12203,7 +12206,7 @@
       <c r="E559" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F559" s="48">
+      <c r="F559" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12221,7 +12224,7 @@
       <c r="E560" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F560" s="48">
+      <c r="F560" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12239,7 +12242,7 @@
       <c r="E561" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F561" s="48">
+      <c r="F561" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12257,7 +12260,7 @@
       <c r="E562" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F562" s="48">
+      <c r="F562" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12275,7 +12278,7 @@
       <c r="E563" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F563" s="48">
+      <c r="F563" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12293,7 +12296,7 @@
       <c r="E564" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F564" s="48">
+      <c r="F564" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12311,7 +12314,7 @@
       <c r="E565" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F565" s="48">
+      <c r="F565" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12329,7 +12332,7 @@
       <c r="E566" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F566" s="48">
+      <c r="F566" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12347,7 +12350,7 @@
       <c r="E567" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F567" s="48">
+      <c r="F567" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12365,7 +12368,7 @@
       <c r="E568" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="F568" s="48">
+      <c r="F568" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12385,7 +12388,7 @@
       <c r="E569" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F569" s="48">
+      <c r="F569" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12403,7 +12406,7 @@
       <c r="E570" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F570" s="48">
+      <c r="F570" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12421,7 +12424,7 @@
       <c r="E571" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F571" s="48">
+      <c r="F571" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12441,7 +12444,7 @@
       <c r="E572" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F572" s="48">
+      <c r="F572" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12459,7 +12462,7 @@
       <c r="E573" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F573" s="48">
+      <c r="F573" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12477,7 +12480,7 @@
       <c r="E574" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="F574" s="48">
+      <c r="F574" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12495,7 +12498,7 @@
       <c r="E575" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F575" s="48">
+      <c r="F575" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12515,7 +12518,7 @@
       <c r="E576" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F576" s="48">
+      <c r="F576" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12533,7 +12536,7 @@
       <c r="E577" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F577" s="48">
+      <c r="F577" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12551,7 +12554,7 @@
       <c r="E578" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F578" s="48">
+      <c r="F578" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12569,7 +12572,7 @@
       <c r="E579" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F579" s="48">
+      <c r="F579" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12587,7 +12590,7 @@
       <c r="E580" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F580" s="48">
+      <c r="F580" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12605,7 +12608,7 @@
       <c r="E581" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F581" s="48">
+      <c r="F581" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12623,7 +12626,7 @@
       <c r="E582" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F582" s="48">
+      <c r="F582" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12641,7 +12644,7 @@
       <c r="E583" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="F583" s="48">
+      <c r="F583" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12659,7 +12662,7 @@
       <c r="E584" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="F584" s="48">
+      <c r="F584" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12677,7 +12680,7 @@
       <c r="E585" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="F585" s="48">
+      <c r="F585" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12695,7 +12698,7 @@
       <c r="E586" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F586" s="48">
+      <c r="F586" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12713,7 +12716,7 @@
       <c r="E587" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F587" s="48">
+      <c r="F587" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12731,7 +12734,7 @@
       <c r="E588" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F588" s="48">
+      <c r="F588" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12749,7 +12752,7 @@
       <c r="E589" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F589" s="48">
+      <c r="F589" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12767,7 +12770,7 @@
       <c r="E590" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F590" s="48">
+      <c r="F590" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12785,7 +12788,7 @@
       <c r="E591" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F591" s="48">
+      <c r="F591" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12805,7 +12808,7 @@
       <c r="E592" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F592" s="48">
+      <c r="F592" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12823,7 +12826,7 @@
       <c r="E593" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="F593" s="48">
+      <c r="F593" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12841,7 +12844,7 @@
       <c r="E594" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F594" s="48">
+      <c r="F594" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12859,7 +12862,7 @@
       <c r="E595" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="F595" s="48">
+      <c r="F595" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12877,7 +12880,7 @@
       <c r="E596" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="F596" s="48">
+      <c r="F596" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12895,7 +12898,7 @@
       <c r="E597" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F597" s="48">
+      <c r="F597" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12915,7 +12918,7 @@
       <c r="E598" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F598" s="48">
+      <c r="F598" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12935,7 +12938,7 @@
       <c r="E599" s="34" t="s">
         <v>298</v>
       </c>
-      <c r="F599" s="48">
+      <c r="F599" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12955,7 +12958,7 @@
       <c r="E600" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F600" s="48">
+      <c r="F600" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12973,7 +12976,7 @@
       <c r="E601" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F601" s="48">
+      <c r="F601" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -12991,7 +12994,7 @@
       <c r="E602" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F602" s="48">
+      <c r="F602" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13009,7 +13012,7 @@
       <c r="E603" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="F603" s="48">
+      <c r="F603" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13027,7 +13030,7 @@
       <c r="E604" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F604" s="48">
+      <c r="F604" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13045,7 +13048,7 @@
       <c r="E605" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F605" s="48">
+      <c r="F605" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13063,7 +13066,7 @@
       <c r="E606" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F606" s="48">
+      <c r="F606" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13081,7 +13084,7 @@
       <c r="E607" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F607" s="48">
+      <c r="F607" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13101,7 +13104,7 @@
       <c r="E608" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="F608" s="48">
+      <c r="F608" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13119,7 +13122,7 @@
       <c r="E609" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F609" s="48">
+      <c r="F609" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13139,7 +13142,7 @@
       <c r="E610" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F610" s="48">
+      <c r="F610" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13157,7 +13160,7 @@
       <c r="E611" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F611" s="48">
+      <c r="F611" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13175,7 +13178,7 @@
       <c r="E612" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F612" s="48">
+      <c r="F612" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13193,7 +13196,7 @@
       <c r="E613" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F613" s="48">
+      <c r="F613" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13213,7 +13216,7 @@
       <c r="E614" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="F614" s="48">
+      <c r="F614" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13231,7 +13234,7 @@
       <c r="E615" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F615" s="48">
+      <c r="F615" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13249,7 +13252,7 @@
       <c r="E616" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F616" s="48">
+      <c r="F616" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13267,7 +13270,7 @@
       <c r="E617" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F617" s="48">
+      <c r="F617" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13285,7 +13288,7 @@
       <c r="E618" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="F618" s="48">
+      <c r="F618" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13303,7 +13306,7 @@
       <c r="E619" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="F619" s="48">
+      <c r="F619" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13321,7 +13324,7 @@
       <c r="E620" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F620" s="48">
+      <c r="F620" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13339,7 +13342,7 @@
       <c r="E621" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F621" s="48">
+      <c r="F621" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13357,7 +13360,7 @@
       <c r="E622" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F622" s="48">
+      <c r="F622" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13377,7 +13380,7 @@
       <c r="E623" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F623" s="48">
+      <c r="F623" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13395,7 +13398,7 @@
       <c r="E624" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F624" s="48">
+      <c r="F624" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13415,7 +13418,7 @@
       <c r="E625" s="37" t="s">
         <v>322</v>
       </c>
-      <c r="F625" s="48">
+      <c r="F625" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13433,7 +13436,7 @@
       <c r="E626" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="F626" s="48">
+      <c r="F626" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13453,7 +13456,7 @@
       <c r="E627" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F627" s="48">
+      <c r="F627" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13473,7 +13476,7 @@
       <c r="E628" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F628" s="48">
+      <c r="F628" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13491,7 +13494,7 @@
       <c r="E629" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F629" s="48">
+      <c r="F629" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13509,7 +13512,7 @@
       <c r="E630" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F630" s="48">
+      <c r="F630" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13529,7 +13532,7 @@
       <c r="E631" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F631" s="48">
+      <c r="F631" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13547,7 +13550,7 @@
       <c r="E632" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F632" s="48">
+      <c r="F632" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13565,7 +13568,7 @@
       <c r="E633" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F633" s="48">
+      <c r="F633" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13583,7 +13586,7 @@
       <c r="E634" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F634" s="48">
+      <c r="F634" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13601,7 +13604,7 @@
       <c r="E635" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F635" s="48">
+      <c r="F635" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13619,7 +13622,7 @@
       <c r="E636" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F636" s="48">
+      <c r="F636" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13637,7 +13640,7 @@
       <c r="E637" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F637" s="48">
+      <c r="F637" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13655,7 +13658,7 @@
       <c r="E638" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F638" s="48">
+      <c r="F638" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13673,7 +13676,7 @@
       <c r="E639" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F639" s="48">
+      <c r="F639" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13691,7 +13694,7 @@
       <c r="E640" s="37" t="s">
         <v>325</v>
       </c>
-      <c r="F640" s="48">
+      <c r="F640" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13711,7 +13714,7 @@
       <c r="E641" s="37" t="s">
         <v>327</v>
       </c>
-      <c r="F641" s="48">
+      <c r="F641" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13729,7 +13732,7 @@
       <c r="E642" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F642" s="48">
+      <c r="F642" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13747,7 +13750,7 @@
       <c r="E643" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F643" s="48">
+      <c r="F643" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13765,7 +13768,7 @@
       <c r="E644" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F644" s="48">
+      <c r="F644" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13783,7 +13786,7 @@
       <c r="E645" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F645" s="48">
+      <c r="F645" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13803,7 +13806,7 @@
       <c r="E646" s="37" t="s">
         <v>330</v>
       </c>
-      <c r="F646" s="48">
+      <c r="F646" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13821,7 +13824,7 @@
       <c r="E647" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F647" s="48">
+      <c r="F647" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13841,7 +13844,7 @@
       <c r="E648" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F648" s="48">
+      <c r="F648" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13859,7 +13862,7 @@
       <c r="E649" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F649" s="48">
+      <c r="F649" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13877,7 +13880,7 @@
       <c r="E650" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F650" s="48">
+      <c r="F650" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13895,7 +13898,7 @@
       <c r="E651" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F651" s="48">
+      <c r="F651" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13913,7 +13916,7 @@
       <c r="E652" s="37" t="s">
         <v>334</v>
       </c>
-      <c r="F652" s="48">
+      <c r="F652" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13931,7 +13934,7 @@
       <c r="E653" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F653" s="48">
+      <c r="F653" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13949,7 +13952,7 @@
       <c r="E654" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F654" s="48">
+      <c r="F654" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13967,7 +13970,7 @@
       <c r="E655" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F655" s="48">
+      <c r="F655" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -13985,7 +13988,7 @@
       <c r="E656" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F656" s="48">
+      <c r="F656" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14003,7 +14006,7 @@
       <c r="E657" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F657" s="48">
+      <c r="F657" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14021,7 +14024,7 @@
       <c r="E658" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F658" s="48">
+      <c r="F658" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14039,7 +14042,7 @@
       <c r="E659" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F659" s="48">
+      <c r="F659" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14057,7 +14060,7 @@
       <c r="E660" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F660" s="48">
+      <c r="F660" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14075,7 +14078,7 @@
       <c r="E661" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F661" s="48">
+      <c r="F661" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14095,7 +14098,7 @@
       <c r="E662" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F662" s="48">
+      <c r="F662" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14113,7 +14116,7 @@
       <c r="E663" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F663" s="48">
+      <c r="F663" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14131,7 +14134,7 @@
       <c r="E664" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F664" s="48">
+      <c r="F664" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14149,7 +14152,7 @@
       <c r="E665" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F665" s="48">
+      <c r="F665" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14167,7 +14170,7 @@
       <c r="E666" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F666" s="48">
+      <c r="F666" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14185,7 +14188,7 @@
       <c r="E667" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F667" s="48">
+      <c r="F667" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14203,7 +14206,7 @@
       <c r="E668" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F668" s="48">
+      <c r="F668" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14221,7 +14224,7 @@
       <c r="E669" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F669" s="48">
+      <c r="F669" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14241,7 +14244,7 @@
       <c r="E670" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F670" s="48">
+      <c r="F670" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14259,7 +14262,7 @@
       <c r="E671" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F671" s="48">
+      <c r="F671" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14277,7 +14280,7 @@
       <c r="E672" s="37" t="s">
         <v>325</v>
       </c>
-      <c r="F672" s="48">
+      <c r="F672" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14295,7 +14298,7 @@
       <c r="E673" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="F673" s="48">
+      <c r="F673" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14313,7 +14316,7 @@
       <c r="E674" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F674" s="48">
+      <c r="F674" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14331,7 +14334,7 @@
       <c r="E675" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F675" s="48">
+      <c r="F675" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14349,7 +14352,7 @@
       <c r="E676" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="F676" s="48">
+      <c r="F676" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14367,7 +14370,7 @@
       <c r="E677" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F677" s="48">
+      <c r="F677" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14385,7 +14388,7 @@
       <c r="E678" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F678" s="48">
+      <c r="F678" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14405,7 +14408,7 @@
       <c r="E679" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F679" s="48">
+      <c r="F679" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14423,7 +14426,7 @@
       <c r="E680" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F680" s="48">
+      <c r="F680" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14441,7 +14444,7 @@
       <c r="E681" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F681" s="48">
+      <c r="F681" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14459,7 +14462,7 @@
       <c r="E682" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F682" s="48">
+      <c r="F682" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14477,7 +14480,7 @@
       <c r="E683" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F683" s="48">
+      <c r="F683" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14497,7 +14500,7 @@
       <c r="E684" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F684" s="48">
+      <c r="F684" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14515,7 +14518,7 @@
       <c r="E685" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F685" s="48">
+      <c r="F685" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14535,7 +14538,7 @@
       <c r="E686" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F686" s="48">
+      <c r="F686" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14553,7 +14556,7 @@
       <c r="E687" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F687" s="48">
+      <c r="F687" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14571,7 +14574,7 @@
       <c r="E688" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F688" s="48">
+      <c r="F688" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14589,7 +14592,7 @@
       <c r="E689" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="F689" s="48">
+      <c r="F689" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14607,7 +14610,7 @@
       <c r="E690" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F690" s="48">
+      <c r="F690" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14625,7 +14628,7 @@
       <c r="E691" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F691" s="48">
+      <c r="F691" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14643,7 +14646,7 @@
       <c r="E692" s="28" t="s">
         <v>325</v>
       </c>
-      <c r="F692" s="48">
+      <c r="F692" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14661,7 +14664,7 @@
       <c r="E693" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="F693" s="48">
+      <c r="F693" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14679,7 +14682,7 @@
       <c r="E694" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F694" s="48">
+      <c r="F694" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14697,7 +14700,7 @@
       <c r="E695" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F695" s="48">
+      <c r="F695" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14715,7 +14718,7 @@
       <c r="E696" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F696" s="48">
+      <c r="F696" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14733,7 +14736,7 @@
       <c r="E697" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F697" s="48">
+      <c r="F697" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14751,7 +14754,7 @@
       <c r="E698" s="28" t="s">
         <v>345</v>
       </c>
-      <c r="F698" s="48">
+      <c r="F698" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14769,7 +14772,7 @@
       <c r="E699" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="F699" s="48">
+      <c r="F699" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14787,7 +14790,7 @@
       <c r="E700" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F700" s="48">
+      <c r="F700" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14807,7 +14810,7 @@
       <c r="E701" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F701" s="48">
+      <c r="F701" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14825,7 +14828,7 @@
       <c r="E702" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F702" s="48">
+      <c r="F702" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14843,7 +14846,7 @@
       <c r="E703" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F703" s="48">
+      <c r="F703" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14861,7 +14864,7 @@
       <c r="E704" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F704" s="48">
+      <c r="F704" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14881,7 +14884,7 @@
       <c r="E705" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="F705" s="48">
+      <c r="F705" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14901,7 +14904,7 @@
       <c r="E706" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="F706" s="48">
+      <c r="F706" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14919,7 +14922,7 @@
       <c r="E707" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F707" s="48">
+      <c r="F707" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14937,7 +14940,7 @@
       <c r="E708" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="F708" s="48">
+      <c r="F708" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14955,7 +14958,7 @@
       <c r="E709" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F709" s="48">
+      <c r="F709" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14973,7 +14976,7 @@
       <c r="E710" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F710" s="48">
+      <c r="F710" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -14991,7 +14994,7 @@
       <c r="E711" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F711" s="48">
+      <c r="F711" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15009,7 +15012,7 @@
       <c r="E712" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F712" s="48">
+      <c r="F712" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15027,7 +15030,7 @@
       <c r="E713" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F713" s="48">
+      <c r="F713" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15045,7 +15048,7 @@
       <c r="E714" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F714" s="48">
+      <c r="F714" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15063,7 +15066,7 @@
       <c r="E715" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F715" s="48">
+      <c r="F715" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15083,7 +15086,7 @@
       <c r="E716" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="F716" s="48">
+      <c r="F716" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15103,7 +15106,7 @@
       <c r="E717" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F717" s="48">
+      <c r="F717" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15123,7 +15126,7 @@
       <c r="E718" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F718" s="48">
+      <c r="F718" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15141,7 +15144,7 @@
       <c r="E719" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F719" s="48">
+      <c r="F719" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15159,7 +15162,7 @@
       <c r="E720" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F720" s="48">
+      <c r="F720" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15177,7 +15180,7 @@
       <c r="E721" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F721" s="48">
+      <c r="F721" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15197,7 +15200,7 @@
       <c r="E722" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="F722" s="48">
+      <c r="F722" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15215,7 +15218,7 @@
       <c r="E723" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F723" s="48">
+      <c r="F723" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15233,7 +15236,7 @@
       <c r="E724" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F724" s="48">
+      <c r="F724" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15251,7 +15254,7 @@
       <c r="E725" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F725" s="48">
+      <c r="F725" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15271,7 +15274,7 @@
       <c r="E726" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="F726" s="48">
+      <c r="F726" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15291,7 +15294,7 @@
       <c r="E727" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F727" s="48">
+      <c r="F727" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15309,7 +15312,7 @@
       <c r="E728" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="F728" s="48">
+      <c r="F728" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15327,7 +15330,7 @@
       <c r="E729" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F729" s="48">
+      <c r="F729" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15345,7 +15348,7 @@
       <c r="E730" t="s">
         <v>7</v>
       </c>
-      <c r="F730" s="48">
+      <c r="F730" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15363,7 +15366,7 @@
       <c r="E731" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F731" s="48">
+      <c r="F731" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15381,7 +15384,7 @@
       <c r="E732" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F732" s="48">
+      <c r="F732" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15399,7 +15402,7 @@
       <c r="E733" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F733" s="48">
+      <c r="F733" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15417,7 +15420,7 @@
       <c r="E734" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F734" s="48">
+      <c r="F734" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15437,7 +15440,7 @@
       <c r="E735" s="37" t="s">
         <v>330</v>
       </c>
-      <c r="F735" s="48">
+      <c r="F735" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15455,7 +15458,7 @@
       <c r="E736" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F736" s="48">
+      <c r="F736" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15475,7 +15478,7 @@
       <c r="E737" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F737" s="48">
+      <c r="F737" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15493,7 +15496,7 @@
       <c r="E738" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F738" s="48">
+      <c r="F738" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15511,7 +15514,7 @@
       <c r="E739" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="F739" s="48">
+      <c r="F739" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15531,7 +15534,7 @@
       <c r="E740" s="32" t="s">
         <v>355</v>
       </c>
-      <c r="F740" s="48">
+      <c r="F740" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15551,7 +15554,7 @@
       <c r="E741" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F741" s="48">
+      <c r="F741" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15569,7 +15572,7 @@
       <c r="E742" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F742" s="48">
+      <c r="F742" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15589,7 +15592,7 @@
       <c r="E743" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F743" s="48">
+      <c r="F743" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15609,7 +15612,7 @@
       <c r="E744" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="F744" s="48">
+      <c r="F744" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15627,7 +15630,7 @@
       <c r="E745" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F745" s="48">
+      <c r="F745" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15645,7 +15648,7 @@
       <c r="E746" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="F746" s="48">
+      <c r="F746" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15663,7 +15666,7 @@
       <c r="E747" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F747" s="48">
+      <c r="F747" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15681,7 +15684,7 @@
       <c r="E748" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F748" s="48">
+      <c r="F748" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15701,7 +15704,7 @@
       <c r="E749" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F749" s="48">
+      <c r="F749" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15719,7 +15722,7 @@
       <c r="E750" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F750" s="48">
+      <c r="F750" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15737,7 +15740,7 @@
       <c r="E751" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F751" s="48">
+      <c r="F751" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15755,7 +15758,7 @@
       <c r="E752" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F752" s="48">
+      <c r="F752" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15775,7 +15778,7 @@
       <c r="E753" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F753" s="48">
+      <c r="F753" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15793,7 +15796,7 @@
       <c r="E754" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F754" s="48">
+      <c r="F754" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15811,7 +15814,7 @@
       <c r="E755" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F755" s="48">
+      <c r="F755" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15829,7 +15832,7 @@
       <c r="E756" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F756" s="48">
+      <c r="F756" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15847,7 +15850,7 @@
       <c r="E757" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F757" s="48">
+      <c r="F757" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15865,7 +15868,7 @@
       <c r="E758" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F758" s="48">
+      <c r="F758" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15883,7 +15886,7 @@
       <c r="E759" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F759" s="48">
+      <c r="F759" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15901,7 +15904,7 @@
       <c r="E760" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F760" s="48">
+      <c r="F760" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15919,7 +15922,7 @@
       <c r="E761" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F761" s="48">
+      <c r="F761" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15937,7 +15940,7 @@
       <c r="E762" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F762" s="48">
+      <c r="F762" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15955,7 +15958,7 @@
       <c r="E763" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F763" s="48">
+      <c r="F763" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15973,7 +15976,7 @@
       <c r="E764" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F764" s="48">
+      <c r="F764" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -15993,7 +15996,7 @@
       <c r="E765" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F765" s="48">
+      <c r="F765" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16011,7 +16014,7 @@
       <c r="E766" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F766" s="48">
+      <c r="F766" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16029,7 +16032,7 @@
       <c r="E767" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F767" s="48">
+      <c r="F767" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16047,7 +16050,7 @@
       <c r="E768" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="F768" s="48">
+      <c r="F768" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16065,7 +16068,7 @@
       <c r="E769" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F769" s="48">
+      <c r="F769" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16083,7 +16086,7 @@
       <c r="E770" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="F770" s="48">
+      <c r="F770" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16101,7 +16104,7 @@
       <c r="E771" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="F771" s="48">
+      <c r="F771" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16121,7 +16124,7 @@
       <c r="E772" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F772" s="48">
+      <c r="F772" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16139,7 +16142,7 @@
       <c r="E773" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="F773" s="48">
+      <c r="F773" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16159,7 +16162,7 @@
       <c r="E774" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F774" s="48">
+      <c r="F774" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16177,7 +16180,7 @@
       <c r="E775" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F775" s="48">
+      <c r="F775" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16197,7 +16200,7 @@
       <c r="E776" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F776" s="48">
+      <c r="F776" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16215,7 +16218,7 @@
       <c r="E777" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F777" s="48">
+      <c r="F777" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16233,7 +16236,7 @@
       <c r="E778" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F778" s="48">
+      <c r="F778" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16251,7 +16254,7 @@
       <c r="E779" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F779" s="48">
+      <c r="F779" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16269,7 +16272,7 @@
       <c r="E780" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F780" s="48">
+      <c r="F780" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16289,7 +16292,7 @@
       <c r="E781" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F781" s="48">
+      <c r="F781" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16307,7 +16310,7 @@
       <c r="E782" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F782" s="48">
+      <c r="F782" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16325,7 +16328,7 @@
       <c r="E783" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F783" s="48">
+      <c r="F783" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16343,7 +16346,7 @@
       <c r="E784" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F784" s="48">
+      <c r="F784" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16361,7 +16364,7 @@
       <c r="E785" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F785" s="48">
+      <c r="F785" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16381,7 +16384,7 @@
       <c r="E786" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F786" s="48">
+      <c r="F786" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16401,7 +16404,7 @@
       <c r="E787" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F787" s="48">
+      <c r="F787" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16419,7 +16422,7 @@
       <c r="E788" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="F788" s="48">
+      <c r="F788" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16437,7 +16440,7 @@
       <c r="E789" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F789" s="48">
+      <c r="F789" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16455,7 +16458,7 @@
       <c r="E790" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F790" s="48">
+      <c r="F790" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16473,7 +16476,7 @@
       <c r="E791" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F791" s="48">
+      <c r="F791" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16491,7 +16494,7 @@
       <c r="E792" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F792" s="48">
+      <c r="F792" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16509,7 +16512,7 @@
       <c r="E793" s="40" t="s">
         <v>365</v>
       </c>
-      <c r="F793" s="48">
+      <c r="F793" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16529,7 +16532,7 @@
       <c r="E794" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F794" s="48">
+      <c r="F794" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16549,7 +16552,7 @@
       <c r="E795" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="F795" s="48">
+      <c r="F795" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16567,7 +16570,7 @@
       <c r="E796" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F796" s="48">
+      <c r="F796" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16585,7 +16588,7 @@
       <c r="E797" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="F797" s="48">
+      <c r="F797" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16603,7 +16606,7 @@
       <c r="E798" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F798" s="48">
+      <c r="F798" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16621,7 +16624,7 @@
       <c r="E799" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F799" s="48">
+      <c r="F799" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16639,7 +16642,7 @@
       <c r="E800" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F800" s="48">
+      <c r="F800" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16657,7 +16660,7 @@
       <c r="E801" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F801" s="48">
+      <c r="F801" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16675,7 +16678,7 @@
       <c r="E802" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F802" s="48">
+      <c r="F802" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16693,7 +16696,7 @@
       <c r="E803" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F803" s="48">
+      <c r="F803" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16711,7 +16714,7 @@
       <c r="E804" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="F804" s="48">
+      <c r="F804" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16729,7 +16732,7 @@
       <c r="E805" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F805" s="48">
+      <c r="F805" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16749,7 +16752,7 @@
       <c r="E806" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="F806" s="48">
+      <c r="F806" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16767,7 +16770,7 @@
       <c r="E807" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F807" s="48">
+      <c r="F807" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16785,7 +16788,7 @@
       <c r="E808" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F808" s="48">
+      <c r="F808" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16803,7 +16806,7 @@
       <c r="E809" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="F809" s="48">
+      <c r="F809" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16821,7 +16824,7 @@
       <c r="E810" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F810" s="48">
+      <c r="F810" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16839,7 +16842,7 @@
       <c r="E811" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F811" s="48">
+      <c r="F811" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16857,7 +16860,7 @@
       <c r="E812" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F812" s="48">
+      <c r="F812" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16875,7 +16878,7 @@
       <c r="E813" s="43" t="s">
         <v>369</v>
       </c>
-      <c r="F813" s="48">
+      <c r="F813" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16893,7 +16896,7 @@
       <c r="E814" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F814" s="48">
+      <c r="F814" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16911,7 +16914,7 @@
       <c r="E815" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="F815" s="48">
+      <c r="F815" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16929,7 +16932,7 @@
       <c r="E816" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F816" s="48">
+      <c r="F816" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16947,7 +16950,7 @@
       <c r="E817" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F817" s="48">
+      <c r="F817" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16965,7 +16968,7 @@
       <c r="E818" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F818" s="48">
+      <c r="F818" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -16985,7 +16988,7 @@
       <c r="E819" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F819" s="48">
+      <c r="F819" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17003,7 +17006,7 @@
       <c r="E820" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="F820" s="48">
+      <c r="F820" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17023,7 +17026,7 @@
       <c r="E821" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="F821" s="48">
+      <c r="F821" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17041,7 +17044,7 @@
       <c r="E822" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F822" s="48">
+      <c r="F822" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17059,7 +17062,7 @@
       <c r="E823" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="F823" s="48">
+      <c r="F823" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17079,7 +17082,7 @@
       <c r="E824" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F824" s="48">
+      <c r="F824" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17099,7 +17102,7 @@
       <c r="E825" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F825" s="48">
+      <c r="F825" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17117,7 +17120,7 @@
       <c r="E826" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F826" s="48">
+      <c r="F826" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17135,7 +17138,7 @@
       <c r="E827" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="F827" s="48">
+      <c r="F827" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17155,7 +17158,7 @@
       <c r="E828" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F828" s="48">
+      <c r="F828" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17173,7 +17176,7 @@
       <c r="E829" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F829" s="48">
+      <c r="F829" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17191,7 +17194,7 @@
       <c r="E830" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F830" s="48">
+      <c r="F830" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17211,7 +17214,7 @@
       <c r="E831" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F831" s="48">
+      <c r="F831" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17229,7 +17232,7 @@
       <c r="E832" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F832" s="48">
+      <c r="F832" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17247,7 +17250,7 @@
       <c r="E833" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F833" s="48">
+      <c r="F833" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17265,7 +17268,7 @@
       <c r="E834" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F834" s="48">
+      <c r="F834" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17283,7 +17286,7 @@
       <c r="E835" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F835" s="48">
+      <c r="F835" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17303,7 +17306,7 @@
       <c r="E836" s="37" t="s">
         <v>330</v>
       </c>
-      <c r="F836" s="48">
+      <c r="F836" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17321,7 +17324,7 @@
       <c r="E837" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F837" s="48">
+      <c r="F837" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17339,7 +17342,7 @@
       <c r="E838" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F838" s="48">
+      <c r="F838" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17359,7 +17362,7 @@
       <c r="E839" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F839" s="48">
+      <c r="F839" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17377,7 +17380,7 @@
       <c r="E840" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F840" s="48">
+      <c r="F840" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17395,7 +17398,7 @@
       <c r="E841" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F841" s="48">
+      <c r="F841" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17415,7 +17418,7 @@
       <c r="E842" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F842" s="48">
+      <c r="F842" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17435,7 +17438,7 @@
       <c r="E843" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F843" s="48">
+      <c r="F843" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17453,7 +17456,7 @@
       <c r="E844" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F844" s="48">
+      <c r="F844" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17471,7 +17474,7 @@
       <c r="E845" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F845" s="48">
+      <c r="F845" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17489,7 +17492,7 @@
       <c r="E846" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F846" s="48">
+      <c r="F846" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17509,7 +17512,7 @@
       <c r="E847" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F847" s="48">
+      <c r="F847" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17527,7 +17530,7 @@
       <c r="E848" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F848" s="48">
+      <c r="F848" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17545,7 +17548,7 @@
       <c r="E849" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F849" s="48">
+      <c r="F849" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17563,7 +17566,7 @@
       <c r="E850" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F850" s="48">
+      <c r="F850" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17581,7 +17584,7 @@
       <c r="E851" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F851" s="48">
+      <c r="F851" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17599,7 +17602,7 @@
       <c r="E852" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="F852" s="48">
+      <c r="F852" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17619,7 +17622,7 @@
       <c r="E853" s="34" t="s">
         <v>377</v>
       </c>
-      <c r="F853" s="48">
+      <c r="F853" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17637,7 +17640,7 @@
       <c r="E854" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F854" s="48">
+      <c r="F854" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17655,7 +17658,7 @@
       <c r="E855" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F855" s="48">
+      <c r="F855" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17673,7 +17676,7 @@
       <c r="E856" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F856" s="48">
+      <c r="F856" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17691,7 +17694,7 @@
       <c r="E857" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F857" s="48">
+      <c r="F857" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17709,7 +17712,7 @@
       <c r="E858" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F858" s="48">
+      <c r="F858" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17727,7 +17730,7 @@
       <c r="E859" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F859" s="48">
+      <c r="F859" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17745,7 +17748,7 @@
       <c r="E860" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F860" s="48">
+      <c r="F860" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17763,7 +17766,7 @@
       <c r="E861" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F861" s="48">
+      <c r="F861" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17781,7 +17784,7 @@
       <c r="E862" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F862" s="48">
+      <c r="F862" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17799,7 +17802,7 @@
       <c r="E863" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F863" s="48">
+      <c r="F863" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17817,7 +17820,7 @@
       <c r="E864" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F864" s="48">
+      <c r="F864" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17837,7 +17840,7 @@
       <c r="E865" s="24" t="s">
         <v>381</v>
       </c>
-      <c r="F865" s="48">
+      <c r="F865" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17855,7 +17858,7 @@
       <c r="E866" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F866" s="48">
+      <c r="F866" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17873,7 +17876,7 @@
       <c r="E867" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F867" s="48">
+      <c r="F867" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17891,7 +17894,7 @@
       <c r="E868" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F868" s="48">
+      <c r="F868" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17909,7 +17912,7 @@
       <c r="E869" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F869" s="48">
+      <c r="F869" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17927,7 +17930,7 @@
       <c r="E870" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F870" s="48">
+      <c r="F870" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17945,7 +17948,7 @@
       <c r="E871" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F871" s="48">
+      <c r="F871" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17963,7 +17966,7 @@
       <c r="E872" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F872" s="48">
+      <c r="F872" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17981,7 +17984,7 @@
       <c r="E873" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F873" s="48">
+      <c r="F873" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -17999,7 +18002,7 @@
       <c r="E874" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F874" s="48">
+      <c r="F874" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18017,7 +18020,7 @@
       <c r="E875" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F875" s="48">
+      <c r="F875" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18037,7 +18040,7 @@
       <c r="E876" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F876" s="48">
+      <c r="F876" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18055,7 +18058,7 @@
       <c r="E877" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F877" s="48">
+      <c r="F877" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18073,7 +18076,7 @@
       <c r="E878" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F878" s="48">
+      <c r="F878" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18091,7 +18094,7 @@
       <c r="E879" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="F879" s="48">
+      <c r="F879" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18109,7 +18112,7 @@
       <c r="E880" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F880" s="48">
+      <c r="F880" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18127,7 +18130,7 @@
       <c r="E881" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F881" s="48">
+      <c r="F881" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18145,7 +18148,7 @@
       <c r="E882" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F882" s="48">
+      <c r="F882" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18165,7 +18168,7 @@
       <c r="E883" s="34" t="s">
         <v>382</v>
       </c>
-      <c r="F883" s="48">
+      <c r="F883" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18183,7 +18186,7 @@
       <c r="E884" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F884" s="48">
+      <c r="F884" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18203,7 +18206,7 @@
       <c r="E885" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F885" s="48">
+      <c r="F885" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18223,7 +18226,7 @@
       <c r="E886" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F886" s="48">
+      <c r="F886" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18241,7 +18244,7 @@
       <c r="E887" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F887" s="48">
+      <c r="F887" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18261,7 +18264,7 @@
       <c r="E888" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F888" s="48">
+      <c r="F888" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18279,7 +18282,7 @@
       <c r="E889" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F889" s="48">
+      <c r="F889" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18297,7 +18300,7 @@
       <c r="E890" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F890" s="48">
+      <c r="F890" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18315,7 +18318,7 @@
       <c r="E891" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F891" s="48">
+      <c r="F891" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18333,7 +18336,7 @@
       <c r="E892" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F892" s="48">
+      <c r="F892" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18351,7 +18354,7 @@
       <c r="E893" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F893" s="48">
+      <c r="F893" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18369,7 +18372,7 @@
       <c r="E894" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F894" s="48">
+      <c r="F894" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18387,7 +18390,7 @@
       <c r="E895" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F895" s="48">
+      <c r="F895" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18405,7 +18408,7 @@
       <c r="E896" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F896" s="48">
+      <c r="F896" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18423,7 +18426,7 @@
       <c r="E897" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F897" s="48">
+      <c r="F897" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18443,7 +18446,7 @@
       <c r="E898" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="F898" s="48">
+      <c r="F898" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18461,7 +18464,7 @@
       <c r="E899" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F899" s="48">
+      <c r="F899" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18479,7 +18482,7 @@
       <c r="E900" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F900" s="48">
+      <c r="F900" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18497,7 +18500,7 @@
       <c r="E901" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F901" s="48">
+      <c r="F901" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18515,7 +18518,7 @@
       <c r="E902" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F902" s="48">
+      <c r="F902" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18533,7 +18536,7 @@
       <c r="E903" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="F903" s="48">
+      <c r="F903" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18551,7 +18554,7 @@
       <c r="E904" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F904" s="48">
+      <c r="F904" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18571,7 +18574,7 @@
       <c r="E905" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="F905" s="48">
+      <c r="F905" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18589,7 +18592,7 @@
       <c r="E906" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F906" s="48">
+      <c r="F906" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18607,7 +18610,7 @@
       <c r="E907" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F907" s="48">
+      <c r="F907" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18625,7 +18628,7 @@
       <c r="E908" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F908" s="48">
+      <c r="F908" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18645,7 +18648,7 @@
       <c r="E909" s="24" t="s">
         <v>388</v>
       </c>
-      <c r="F909" s="48">
+      <c r="F909" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18665,7 +18668,7 @@
       <c r="E910" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F910" s="48">
+      <c r="F910" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18685,7 +18688,7 @@
       <c r="E911" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F911" s="48">
+      <c r="F911" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18703,7 +18706,7 @@
       <c r="E912" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F912" s="48">
+      <c r="F912" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18721,7 +18724,7 @@
       <c r="E913" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F913" s="48">
+      <c r="F913" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18739,7 +18742,7 @@
       <c r="E914" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="F914" s="48">
+      <c r="F914" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18757,7 +18760,7 @@
       <c r="E915" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F915" s="48">
+      <c r="F915" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18777,7 +18780,7 @@
       <c r="E916" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="F916" s="48">
+      <c r="F916" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18795,7 +18798,7 @@
       <c r="E917" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F917" s="48">
+      <c r="F917" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18813,7 +18816,7 @@
       <c r="E918" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F918" s="48">
+      <c r="F918" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18833,7 +18836,7 @@
       <c r="E919" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F919" s="48">
+      <c r="F919" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18851,7 +18854,7 @@
       <c r="E920" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F920" s="48">
+      <c r="F920" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18869,7 +18872,7 @@
       <c r="E921" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F921" s="48">
+      <c r="F921" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18887,7 +18890,7 @@
       <c r="E922" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F922" s="48">
+      <c r="F922" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18905,7 +18908,7 @@
       <c r="E923" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F923" s="48">
+      <c r="F923" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18923,7 +18926,7 @@
       <c r="E924" s="42" t="s">
         <v>392</v>
       </c>
-      <c r="F924" s="48">
+      <c r="F924" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18941,7 +18944,7 @@
       <c r="E925" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F925" s="48">
+      <c r="F925" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18961,7 +18964,7 @@
       <c r="E926" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F926" s="48">
+      <c r="F926" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18979,7 +18982,7 @@
       <c r="E927" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F927" s="48">
+      <c r="F927" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -18997,7 +19000,7 @@
       <c r="E928" s="46" t="s">
         <v>269</v>
       </c>
-      <c r="F928" s="48">
+      <c r="F928" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19015,7 +19018,7 @@
       <c r="E929" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F929" s="48">
+      <c r="F929" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19033,7 +19036,7 @@
       <c r="E930" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F930" s="48">
+      <c r="F930" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19053,7 +19056,7 @@
       <c r="E931" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F931" s="48">
+      <c r="F931" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19073,7 +19076,7 @@
       <c r="E932" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="F932" s="48">
+      <c r="F932" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19091,7 +19094,7 @@
       <c r="E933" s="43" t="s">
         <v>269</v>
       </c>
-      <c r="F933" s="48">
+      <c r="F933" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19109,7 +19112,7 @@
       <c r="E934" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F934" s="48">
+      <c r="F934" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19127,7 +19130,7 @@
       <c r="E935" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F935" s="48">
+      <c r="F935" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19145,7 +19148,7 @@
       <c r="E936" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="F936" s="48">
+      <c r="F936" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19163,7 +19166,7 @@
       <c r="E937" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F937" s="48">
+      <c r="F937" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19181,7 +19184,7 @@
       <c r="E938" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="F938" s="48">
+      <c r="F938" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19199,7 +19202,7 @@
       <c r="E939" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F939" s="48">
+      <c r="F939" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19217,7 +19220,7 @@
       <c r="E940" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F940" s="48">
+      <c r="F940" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19235,7 +19238,7 @@
       <c r="E941" s="43" t="s">
         <v>269</v>
       </c>
-      <c r="F941" s="48">
+      <c r="F941" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19253,7 +19256,7 @@
       <c r="E942" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="F942" s="48">
+      <c r="F942" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19271,7 +19274,7 @@
       <c r="E943" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="F943" s="48">
+      <c r="F943" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19289,7 +19292,7 @@
       <c r="E944" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="F944" s="48">
+      <c r="F944" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19307,7 +19310,7 @@
       <c r="E945" s="43" t="s">
         <v>269</v>
       </c>
-      <c r="F945" s="48">
+      <c r="F945" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19325,7 +19328,7 @@
       <c r="E946" s="42" t="s">
         <v>269</v>
       </c>
-      <c r="F946" s="48">
+      <c r="F946" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19343,7 +19346,7 @@
       <c r="E947" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F947" s="48">
+      <c r="F947" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19361,7 +19364,7 @@
       <c r="E948" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F948" s="48">
+      <c r="F948" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19381,7 +19384,7 @@
       <c r="E949" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F949" s="48">
+      <c r="F949" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19399,7 +19402,7 @@
       <c r="E950" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F950" s="48">
+      <c r="F950" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19417,7 +19420,7 @@
       <c r="E951" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F951" s="48">
+      <c r="F951" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19435,7 +19438,7 @@
       <c r="E952" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="F952" s="48">
+      <c r="F952" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19455,7 +19458,7 @@
       <c r="E953" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="F953" s="48">
+      <c r="F953" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19473,7 +19476,7 @@
       <c r="E954" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="F954" s="48">
+      <c r="F954" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19491,7 +19494,7 @@
       <c r="E955" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="F955" s="48">
+      <c r="F955" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19509,7 +19512,7 @@
       <c r="E956" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F956" s="48">
+      <c r="F956" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19529,7 +19532,7 @@
       <c r="E957" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F957" s="48">
+      <c r="F957" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19547,7 +19550,7 @@
       <c r="E958" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F958" s="48">
+      <c r="F958" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19565,7 +19568,7 @@
       <c r="E959" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F959" s="48">
+      <c r="F959" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19583,7 +19586,7 @@
       <c r="E960" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F960" s="48">
+      <c r="F960" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19601,7 +19604,7 @@
       <c r="E961" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F961" s="48">
+      <c r="F961" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19619,7 +19622,7 @@
       <c r="E962" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F962" s="48">
+      <c r="F962" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19637,7 +19640,7 @@
       <c r="E963" t="s">
         <v>398</v>
       </c>
-      <c r="F963" s="48">
+      <c r="F963" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19655,7 +19658,7 @@
       <c r="E964" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F964" s="48">
+      <c r="F964" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19673,7 +19676,7 @@
       <c r="E965" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F965" s="48">
+      <c r="F965" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19693,7 +19696,7 @@
       <c r="E966" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F966" s="48">
+      <c r="F966" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19713,7 +19716,7 @@
       <c r="E967" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F967" s="48">
+      <c r="F967" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19731,7 +19734,7 @@
       <c r="E968" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="F968" s="48">
+      <c r="F968" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19749,7 +19752,7 @@
       <c r="E969" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F969" s="48">
+      <c r="F969" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19767,7 +19770,7 @@
       <c r="E970" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F970" s="48">
+      <c r="F970" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19785,7 +19788,7 @@
       <c r="E971" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F971" s="48">
+      <c r="F971" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19803,7 +19806,7 @@
       <c r="E972" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="F972" s="48">
+      <c r="F972" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19823,7 +19826,7 @@
       <c r="E973" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F973" s="48">
+      <c r="F973" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19841,7 +19844,7 @@
       <c r="E974" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F974" s="48">
+      <c r="F974" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19859,7 +19862,7 @@
       <c r="E975" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F975" s="48">
+      <c r="F975" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19877,7 +19880,7 @@
       <c r="E976" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F976" s="48">
+      <c r="F976" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19897,7 +19900,7 @@
       <c r="E977" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="F977" s="48">
+      <c r="F977" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19915,7 +19918,7 @@
       <c r="E978" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F978" s="48">
+      <c r="F978" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19933,7 +19936,7 @@
       <c r="E979" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F979" s="48">
+      <c r="F979" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19951,7 +19954,7 @@
       <c r="E980" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F980" s="48">
+      <c r="F980" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19969,7 +19972,7 @@
       <c r="E981" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F981" s="48">
+      <c r="F981" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -19987,7 +19990,7 @@
       <c r="E982" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F982" s="48">
+      <c r="F982" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20005,7 +20008,7 @@
       <c r="E983" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F983" s="48">
+      <c r="F983" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20023,7 +20026,7 @@
       <c r="E984" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F984" s="48">
+      <c r="F984" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20041,7 +20044,7 @@
       <c r="E985" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F985" s="48">
+      <c r="F985" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20061,7 +20064,7 @@
       <c r="E986" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F986" s="48">
+      <c r="F986" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20079,7 +20082,7 @@
       <c r="E987" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F987" s="48">
+      <c r="F987" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20099,7 +20102,7 @@
       <c r="E988" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F988" s="48">
+      <c r="F988" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20117,7 +20120,7 @@
       <c r="E989" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F989" s="48">
+      <c r="F989" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20135,7 +20138,7 @@
       <c r="E990" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F990" s="48">
+      <c r="F990" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20153,7 +20156,7 @@
       <c r="E991" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F991" s="48">
+      <c r="F991" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20171,7 +20174,7 @@
       <c r="E992" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F992" s="48">
+      <c r="F992" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20189,7 +20192,7 @@
       <c r="E993" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="F993" s="48">
+      <c r="F993" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20207,7 +20210,7 @@
       <c r="E994" t="s">
         <v>44</v>
       </c>
-      <c r="F994" s="48">
+      <c r="F994" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20225,7 +20228,7 @@
       <c r="E995" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F995" s="48">
+      <c r="F995" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20243,7 +20246,7 @@
       <c r="E996" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F996" s="48">
+      <c r="F996" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20261,7 +20264,7 @@
       <c r="E997" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F997" s="48">
+      <c r="F997" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20281,7 +20284,7 @@
       <c r="E998" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F998" s="48">
+      <c r="F998" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20301,7 +20304,7 @@
       <c r="E999" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F999" s="48">
+      <c r="F999" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20319,7 +20322,7 @@
       <c r="E1000" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F1000" s="48">
+      <c r="F1000" s="49">
         <v>46143</v>
       </c>
     </row>
@@ -20337,7 +20340,7 @@
       <c r="E1001" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F1001" s="48">
+      <c r="F1001" s="49">
         <v>46143</v>
       </c>
     </row>

--- a/data.xlsx.xlsx
+++ b/data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yana.k\.cursor\projects\empty-window\nps-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCAE778-7BAA-432E-A68C-9D19BD6CE420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52503D2-9878-47B0-833E-9A164FFD7DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{74487427-0345-4DD6-8246-25E85D8ABC71}"/>
   </bookViews>
@@ -1258,7 +1258,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-419]mmmm\ yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-419]mmmm;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1274,6 +1274,8 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1292,12 +1294,15 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1553,16 +1558,16 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
